--- a/Luban/Excel/事件影响.xlsx
+++ b/Luban/Excel/事件影响.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
     <t>竹仅风交互覆盖为事件对话</t>
   </si>
   <si>
-    <t>竹仅风活动</t>
+    <t>竹仅风活动变为除外</t>
   </si>
 </sst>
 </file>
